--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/persona/primary_persona_vs_mobile_review_display.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/persona/primary_persona_vs_mobile_review_display.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
